--- a/data/trans_dic/P1426-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1426-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,04</t>
+          <t>0,5; 3,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,26</t>
+          <t>2,82; 5,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,95</t>
+          <t>0,35; 3,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,57</t>
+          <t>0,62; 3,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,69</t>
+          <t>2,22; 4,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,52</t>
+          <t>0,26; 1,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,75</t>
+          <t>0,75; 2,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,86</t>
+          <t>2,83; 4,93</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,11</t>
+          <t>0,46; 2,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,65</t>
+          <t>3,25; 6,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,95</t>
+          <t>0,59; 3,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,48</t>
+          <t>0,25; 3,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,77</t>
+          <t>1,27; 3,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,65</t>
+          <t>0,67; 2,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,07</t>
+          <t>0,28; 2,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,94</t>
+          <t>2,61; 4,77</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,54</t>
+          <t>1,0; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,37</t>
+          <t>0,9; 3,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,79</t>
+          <t>3,16; 6,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,92</t>
+          <t>0,41; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,67</t>
+          <t>0,68; 6,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,04</t>
+          <t>2,16; 6,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,13</t>
+          <t>1,13; 3,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,32</t>
+          <t>1,21; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,39</t>
+          <t>3,29; 6,02</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,66</t>
+          <t>1,05; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,7</t>
+          <t>1,03; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,2</t>
+          <t>0,4; 2,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,34</t>
+          <t>0,75; 2,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,6</t>
+          <t>2,41; 4,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,05</t>
+          <t>0,95; 2,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,12</t>
+          <t>1,06; 2,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,27</t>
+          <t>3,93; 5,63</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,21</t>
+          <t>1,39; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,36</t>
+          <t>1,13; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,11</t>
+          <t>3,23; 6,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,67</t>
+          <t>0,73; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,98</t>
+          <t>0,88; 2,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,39</t>
+          <t>5,47; 8,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,68</t>
+          <t>1,25; 2,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,73</t>
+          <t>1,19; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,89</t>
+          <t>4,91; 6,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,28</t>
+          <t>0,21; 2,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,11</t>
+          <t>2,06; 4,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,32</t>
+          <t>2,05; 4,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,3</t>
+          <t>5,24; 8,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,46</t>
+          <t>1,75; 3,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,41</t>
+          <t>1,73; 3,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,52</t>
+          <t>4,19; 6,51</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,06</t>
+          <t>1,15; 2,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,88</t>
+          <t>1,08; 1,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,29</t>
+          <t>4,09; 5,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,4</t>
+          <t>1,45; 2,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,59</t>
+          <t>1,6; 2,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,98</t>
+          <t>4,15; 5,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,39; 2,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,11</t>
+          <t>1,43; 2,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 4,97</t>
+          <t>4,28; 5,11</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>39313</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5290</t>
+          <t>0; 5228</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1962; 13038</t>
+          <t>2142; 14064</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14665; 31631</t>
+          <t>15532; 32921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1033; 9270</t>
+          <t>1110; 9716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2085; 12376</t>
+          <t>2141; 12470</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8954; 20984</t>
+          <t>10853; 24300</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1998; 11394</t>
+          <t>1982; 11376</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5948; 21351</t>
+          <t>5794; 20069</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26635; 46336</t>
+          <t>29360; 51214</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30452</t>
+          <t>32055</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1965; 13012</t>
+          <t>1907; 12190</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6355</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14628; 30070</t>
+          <t>15685; 31457</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1917; 13346</t>
+          <t>2000; 13059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>929; 12942</t>
+          <t>930; 12306</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4824; 14373</t>
+          <t>5344; 14823</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5063; 20033</t>
+          <t>5100; 20345</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2029; 15518</t>
+          <t>2091; 15541</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22423; 41211</t>
+          <t>23603; 43189</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>29989</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6407; 22283</t>
+          <t>6299; 22628</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4673; 17568</t>
+          <t>4711; 17111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7300; 38621</t>
+          <t>14887; 32026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1073; 10206</t>
+          <t>1069; 9772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1100; 11074</t>
+          <t>1121; 10545</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4159; 11755</t>
+          <t>4050; 12923</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10048; 27877</t>
+          <t>10082; 29090</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7437; 22835</t>
+          <t>8292; 23307</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11933; 44966</t>
+          <t>21665; 39625</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86950</t>
+          <t>94521</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12081; 30856</t>
+          <t>12180; 31433</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11932; 31090</t>
+          <t>11837; 30022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49544; 76366</t>
+          <t>54215; 83511</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3814; 16819</t>
+          <t>3033; 15608</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5891; 19339</t>
+          <t>6170; 20379</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11580; 35167</t>
+          <t>20739; 35751</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18005; 39518</t>
+          <t>18328; 41270</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20912; 41935</t>
+          <t>20887; 42225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58830; 105965</t>
+          <t>78310; 112135</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24512</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75342</t>
+          <t>79913</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7092; 21475</t>
+          <t>7112; 20779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7457; 20847</t>
+          <t>7018; 20822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16926; 33708</t>
+          <t>18294; 35000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5934; 20270</t>
+          <t>5537; 20179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6912; 21991</t>
+          <t>6484; 21054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36488; 61936</t>
+          <t>45332; 66350</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15081; 34016</t>
+          <t>15859; 34582</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17082; 37045</t>
+          <t>16200; 36549</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59861; 90388</t>
+          <t>68566; 93337</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51838</t>
+          <t>56058</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9551</t>
+          <t>0; 8580</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>462; 5491</t>
+          <t>500; 6062</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21973; 45647</t>
+          <t>22901; 47489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22936; 46754</t>
+          <t>22185; 46023</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40023; 63149</t>
+          <t>44210; 67598</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24056; 47565</t>
+          <t>24025; 48816</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22228; 46693</t>
+          <t>23718; 48206</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41948; 65269</t>
+          <t>45318; 70355</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152659</t>
+          <t>161813</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>156279</t>
+          <t>170037</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>308938</t>
+          <t>331850</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>40376; 70440</t>
+          <t>39301; 73525</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37334; 63507</t>
+          <t>36676; 64464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117504; 178497</t>
+          <t>140832; 184921</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49754; 85079</t>
+          <t>51360; 83050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>56755; 91456</t>
+          <t>56542; 94505</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>124387; 178053</t>
+          <t>150518; 190422</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98049; 143457</t>
+          <t>96609; 141415</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99665; 145998</t>
+          <t>99142; 144484</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>262006; 344892</t>
+          <t>302899; 361366</t>
         </is>
       </c>
     </row>
